--- a/artfynd/A 1188-2024 artfynd.xlsx
+++ b/artfynd/A 1188-2024 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 1188-2024 artfynd.xlsx
+++ b/artfynd/A 1188-2024 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>64330449</v>
       </c>
       <c r="B2" t="n">
-        <v>98537</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100786</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>434878.3160316468</v>
+        <v>434878</v>
       </c>
       <c r="R2" t="n">
-        <v>6213792.496294236</v>
+        <v>6213792</v>
       </c>
       <c r="S2" t="n">
         <v>100</v>
@@ -748,19 +743,9 @@
           <t>2000-05-02</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2000-05-02</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">

--- a/artfynd/A 1188-2024 artfynd.xlsx
+++ b/artfynd/A 1188-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>64330449</v>
       </c>
       <c r="B2" t="n">
-        <v>100786</v>
+        <v>100791</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 1188-2024 artfynd.xlsx
+++ b/artfynd/A 1188-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>64330449</v>
       </c>
       <c r="B2" t="n">
-        <v>100791</v>
+        <v>100797</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 1188-2024 artfynd.xlsx
+++ b/artfynd/A 1188-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>64330449</v>
       </c>
       <c r="B2" t="n">
-        <v>100797</v>
+        <v>100798</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 1188-2024 artfynd.xlsx
+++ b/artfynd/A 1188-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>64330449</v>
       </c>
       <c r="B2" t="n">
-        <v>100798</v>
+        <v>100825</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 1188-2024 artfynd.xlsx
+++ b/artfynd/A 1188-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>64330449</v>
       </c>
       <c r="B2" t="n">
-        <v>100825</v>
+        <v>100831</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 1188-2024 artfynd.xlsx
+++ b/artfynd/A 1188-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>64330449</v>
       </c>
       <c r="B2" t="n">
-        <v>100831</v>
+        <v>100838</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 1188-2024 artfynd.xlsx
+++ b/artfynd/A 1188-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>64330449</v>
       </c>
       <c r="B2" t="n">
-        <v>100838</v>
+        <v>100842</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 1188-2024 artfynd.xlsx
+++ b/artfynd/A 1188-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>64330449</v>
       </c>
       <c r="B2" t="n">
-        <v>100842</v>
+        <v>100849</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 1188-2024 artfynd.xlsx
+++ b/artfynd/A 1188-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>64330449</v>
       </c>
       <c r="B2" t="n">
-        <v>100852</v>
+        <v>100857</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 1188-2024 artfynd.xlsx
+++ b/artfynd/A 1188-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>64330449</v>
       </c>
       <c r="B2" t="n">
-        <v>100857</v>
+        <v>100865</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 1188-2024 artfynd.xlsx
+++ b/artfynd/A 1188-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>64330449</v>
       </c>
       <c r="B2" t="n">
-        <v>100865</v>
+        <v>100875</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 1188-2024 artfynd.xlsx
+++ b/artfynd/A 1188-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>64330449</v>
+        <v>6287876</v>
       </c>
       <c r="B2" t="n">
-        <v>100875</v>
+        <v>100933</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,37 +686,42 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222886</v>
+        <v>224913</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Backsippa</t>
+          <t>Vanlig backsippa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pulsatilla vulgaris</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Mill.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>Pulsatilla vulgaris subsp. vulgaris</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>500m NO Fåglasång, Sk</t>
+          <t>Fåglasång, 350 m NO, Sk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>434878</v>
+        <v>434880</v>
       </c>
       <c r="R2" t="n">
-        <v>6213792</v>
+        <v>6213593</v>
       </c>
       <c r="S2" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -738,19 +743,24 @@
           <t>Önnestad</t>
         </is>
       </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>M-Kri-0104</t>
+        </is>
+      </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2000-05-02</t>
+          <t>2000-05-19</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2000-05-02</t>
+          <t>2000-05-19</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Pulsatilla vulgaris/3D3g1747/Önnestad s:n/THm/ /Tord Holm,Hässleholm</t>
+          <t>3D3g1547, 3D3g1747, Tord Holm</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -764,26 +774,137 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>vägren, 2 ex</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>SkFlora    598079</t>
+          <t>gräsmark</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Skåne Floraväktarna</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Via Skåne Floraväktarna</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>64330449</v>
+      </c>
+      <c r="B3" t="n">
+        <v>100875</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>222886</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Backsippa</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Pulsatilla vulgaris</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Mill.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>500m NO Fåglasång, Sk</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>434878</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6213792</v>
+      </c>
+      <c r="S3" t="n">
+        <v>100</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Kristianstad</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Önnestad</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2000-05-02</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2000-05-02</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Pulsatilla vulgaris/3D3g1747/Önnestad s:n/THm/ /Tord Holm,Hässleholm</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>vägren, 2 ex</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>SkFlora    598079</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
           <t>Charlotte Wigermo</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX3" t="inlineStr">
         <is>
           <t>Via Charlotte Wigermo</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr">
+      <c r="AY3" t="inlineStr">
         <is>
           <t>Skånes Flora (1989-2006)</t>
         </is>

--- a/artfynd/A 1188-2024 artfynd.xlsx
+++ b/artfynd/A 1188-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>6287876</v>
       </c>
       <c r="B2" t="n">
-        <v>100933</v>
+        <v>100936</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 1188-2024 artfynd.xlsx
+++ b/artfynd/A 1188-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>6287876</v>
       </c>
       <c r="B2" t="n">
-        <v>100936</v>
+        <v>100965</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 1188-2024 artfynd.xlsx
+++ b/artfynd/A 1188-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>6287876</v>
       </c>
       <c r="B2" t="n">
-        <v>100965</v>
+        <v>100977</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 1188-2024 artfynd.xlsx
+++ b/artfynd/A 1188-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>6287876</v>
       </c>
       <c r="B2" t="n">
-        <v>100977</v>
+        <v>100978</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 1188-2024 artfynd.xlsx
+++ b/artfynd/A 1188-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>6287876</v>
       </c>
       <c r="B2" t="n">
-        <v>100978</v>
+        <v>100983</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 1188-2024 artfynd.xlsx
+++ b/artfynd/A 1188-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>6287876</v>
       </c>
       <c r="B2" t="n">
-        <v>100983</v>
+        <v>100987</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 1188-2024 artfynd.xlsx
+++ b/artfynd/A 1188-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>6287876</v>
       </c>
       <c r="B2" t="n">
-        <v>100987</v>
+        <v>100989</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 1188-2024 artfynd.xlsx
+++ b/artfynd/A 1188-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>6287876</v>
       </c>
       <c r="B2" t="n">
-        <v>100989</v>
+        <v>100999</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 1188-2024 artfynd.xlsx
+++ b/artfynd/A 1188-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>6287876</v>
+        <v>64330449</v>
       </c>
       <c r="B2" t="n">
-        <v>100999</v>
+        <v>101345</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,42 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>224913</v>
+        <v>222886</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vanlig backsippa</t>
+          <t>Backsippa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pulsatilla vulgaris subsp. vulgaris</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Pulsatilla vulgaris</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Mill.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Fåglasång, 350 m NO, Sk</t>
+          <t>500m NO Fåglasång, Sk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>434880</v>
+        <v>434878</v>
       </c>
       <c r="R2" t="n">
-        <v>6213593</v>
+        <v>6213792</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -743,24 +738,19 @@
           <t>Önnestad</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>M-Kri-0104</t>
-        </is>
-      </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2000-05-19</t>
+          <t>2000-05-02</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2000-05-19</t>
+          <t>2000-05-02</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>3D3g1547, 3D3g1747, Tord Holm</t>
+          <t>Pulsatilla vulgaris/3D3g1747/Önnestad s:n/THm/ /Tord Holm,Hässleholm</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -774,32 +764,37 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>gräsmark</t>
+          <t>vägren, 2 ex</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>SkFlora    598079</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Skåne Floraväktarna</t>
+          <t>Charlotte Wigermo</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Via Skåne Floraväktarna</t>
+          <t>Via Charlotte Wigermo</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>Floraväkteri Sverige</t>
+          <t>Skånes Flora (1989-2006)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>64330449</v>
+        <v>6287876</v>
       </c>
       <c r="B3" t="n">
-        <v>100875</v>
+        <v>101347</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,37 +802,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222886</v>
+        <v>224913</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Backsippa</t>
+          <t>Vanlig backsippa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pulsatilla vulgaris</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Mill.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>Pulsatilla vulgaris subsp. vulgaris</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>500m NO Fåglasång, Sk</t>
+          <t>Fåglasång, 350 m NO, Sk</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>434878</v>
+        <v>434880</v>
       </c>
       <c r="R3" t="n">
-        <v>6213792</v>
+        <v>6213593</v>
       </c>
       <c r="S3" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -859,19 +859,24 @@
           <t>Önnestad</t>
         </is>
       </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>M-Kri-0104</t>
+        </is>
+      </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2000-05-02</t>
+          <t>2000-05-19</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2000-05-02</t>
+          <t>2000-05-19</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Pulsatilla vulgaris/3D3g1747/Önnestad s:n/THm/ /Tord Holm,Hässleholm</t>
+          <t>3D3g1547, 3D3g1747, Tord Holm</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -885,28 +890,23 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>vägren, 2 ex</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>SkFlora    598079</t>
+          <t>gräsmark</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Charlotte Wigermo</t>
+          <t>Skåne Floraväktarna</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Via Charlotte Wigermo</t>
+          <t>Via Skåne Floraväktarna</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>Skånes Flora (1989-2006)</t>
+          <t>Floraväkteri Sverige</t>
         </is>
       </c>
     </row>

--- a/artfynd/A 1188-2024 artfynd.xlsx
+++ b/artfynd/A 1188-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -788,6 +793,11 @@
           <t>Skånes Flora (1989-2006)</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/64330449</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -909,8 +919,17 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6287876</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>